--- a/jogos_2024-11-25.xlsx
+++ b/jogos_2024-11-25.xlsx
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,19 +1933,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD12" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['3', '50', '54', '78', '84']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.59</v>
+        <v>3.4</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45621.58333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.4</v>
       </c>
-      <c r="M13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="X13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.95</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X13" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['3', '50', '54', '78', '84']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45621.58333333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
         <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
         <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z16" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA16" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['45', '52']</t>
+          <t>['19', '45+3']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['20', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45621.625</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>3.1</v>
-      </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="P17" t="n">
         <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
         <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z17" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA17" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['45', '52']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['20', '77']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AH17" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['19', '45+3']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>1.62</v>
       </c>
-      <c r="AH17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45621.625</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.88</v>
+        <v>5.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.94</v>
+        <v>6.14</v>
       </c>
       <c r="O20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD20" t="n">
         <v>2.63</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['17', '42', '90+8']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>3.25</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['5', '9', '47']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45621.66666666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.25</v>
       </c>
-      <c r="M21" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.6</v>
-      </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
         <v>1.2</v>
       </c>
       <c r="S21" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="U21" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="Z21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>3.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['4', '82']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['43']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45621.66666666666</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>2</v>
       </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.13</v>
+        <v>2.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.62</v>
+        <v>3.88</v>
       </c>
       <c r="N22" t="n">
-        <v>2.17</v>
+        <v>2.94</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2.75</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['69', '89']</t>
+          <t>['5', '9', '47']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45621.66666666666</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,55 +3378,55 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.43</v>
+        <v>3.13</v>
       </c>
       <c r="M23" t="n">
-        <v>5.06</v>
+        <v>3.62</v>
       </c>
       <c r="N23" t="n">
-        <v>6.04</v>
+        <v>2.17</v>
       </c>
       <c r="O23" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q23" t="n">
-        <v>5.5</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
         <v>1.57</v>
@@ -3436,25 +3436,25 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['45+2', '64']</t>
+          <t>['69', '89']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['72', '76']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.8</v>
+        <v>1.38</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45621.66666666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>5.06</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>6.04</v>
       </c>
       <c r="O24" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
         <v>1.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['45+2', '64']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['72', '76']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45621.66666666666</v>
@@ -3739,109 +3739,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.83</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
         <v>7.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['17', '42', '90+8']</t>
+          <t>['4', '82']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.12</v>
+        <v>1.52</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45621.66666666666</v>
@@ -3868,48 +3868,48 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lucchese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O27" t="n">
         <v>2</v>
       </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.88</v>
-      </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="R27" t="n">
         <v>1.44</v>
@@ -3918,59 +3918,59 @@
         <v>2.63</v>
       </c>
       <c r="T27" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.33</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['7', '67']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45621.6875</v>
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Lucchese</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,22 +4023,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="N28" t="n">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q28" t="n">
-        <v>6.5</v>
+        <v>3.75</v>
       </c>
       <c r="R28" t="n">
         <v>1.44</v>
@@ -4047,59 +4047,59 @@
         <v>2.63</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X28" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '67']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.29</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45621.6875</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['70']</t>
-        </is>
-      </c>
       <c r="AG30" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45621.69791666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,22 +4384,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y31" t="n">
         <v>2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Z31" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45621.69791666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y32" t="n">
         <v>2</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N32" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O32" t="n">
+      <c r="Z32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC32" t="n">
         <v>2</v>
       </c>
-      <c r="P32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="AD32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.53</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['10', '53']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45621.70833333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="O33" t="n">
+        <v>2</v>
+      </c>
+      <c r="P33" t="n">
         <v>2.5</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="V33" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="X33" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['10', '53']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.95</v>
+        <v>2.68</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45621.70833333334</v>
@@ -4761,35 +4761,35 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sol de América</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M34" t="n">
         <v>3.3</v>
@@ -4806,74 +4806,74 @@
         <v>2.75</v>
       </c>
       <c r="O34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q34" t="n">
         <v>3.2</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.6</v>
-      </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S34" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="T34" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
         <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W34" t="n">
         <v>1.36</v>
       </c>
       <c r="X34" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z34" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AA34" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AB34" t="n">
         <v>1.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['67', '76']</t>
+          <t>['40', '60']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AI34" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45621.79166666666</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,19 +4900,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Central Córdoba SdE</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Sol de América</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M35" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T35" t="n">
         <v>3.25</v>
       </c>
-      <c r="P35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>4</v>
-      </c>
       <c r="U35" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V35" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="X35" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AA35" t="n">
-        <v>5.87</v>
+        <v>3.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
+          <t>['67', '76']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['90']</t>
-        </is>
-      </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45621.79166666666</v>
@@ -5277,35 +5277,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>2.75</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['40', '60']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['24']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45621.79166666666</v>
@@ -5416,19 +5416,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -5442,22 +5442,22 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="O39" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="P39" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q39" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="R39" t="n">
         <v>1.57</v>
@@ -5472,25 +5472,25 @@
         <v>1.25</v>
       </c>
       <c r="V39" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z39" t="n">
         <v>1.48</v>
       </c>
-      <c r="X39" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AA39" t="n">
-        <v>4.81</v>
+        <v>4.93</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC39" t="n">
         <v>2.25</v>
@@ -5505,20 +5505,20 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['26', '67']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AJ39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45621.88541666666</v>
@@ -5545,19 +5545,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -5571,22 +5571,22 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="M40" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="O40" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="P40" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="R40" t="n">
         <v>1.57</v>
@@ -5601,25 +5601,25 @@
         <v>1.25</v>
       </c>
       <c r="V40" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X40" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.93</v>
+        <v>4.81</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AC40" t="n">
         <v>2.25</v>
@@ -5634,20 +5634,20 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>['26', '67']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AJ40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45621.88541666666</v>
